--- a/salidas/empresas/AXP.xlsx
+++ b/salidas/empresas/AXP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>38.62009429931641</v>
+        <v>38.6201057434082</v>
       </c>
       <c r="C2" t="n">
         <v>52.45000076293945</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.6937255859375</v>
+        <v>38.6937370300293</v>
       </c>
       <c r="C4" t="n">
         <v>52.54999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.71101379394531</v>
+        <v>39.71100616455078</v>
       </c>
       <c r="C5" t="n">
         <v>53.81000137329102</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.11688613891602</v>
+        <v>40.11688995361328</v>
       </c>
       <c r="C6" t="n">
         <v>54.36000061035156</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.5272331237793</v>
+        <v>38.52722930908203</v>
       </c>
       <c r="C8" t="n">
         <v>52.06000137329102</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.88245391845703</v>
+        <v>38.8824577331543</v>
       </c>
       <c r="C9" t="n">
         <v>52.54000091552734</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>41.50225830078125</v>
+        <v>41.50226974487305</v>
       </c>
       <c r="C10" t="n">
         <v>56.08000183105469</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>42.89747619628906</v>
+        <v>42.89748001098633</v>
       </c>
       <c r="C11" t="n">
         <v>57.81000137329102</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>43.57273483276367</v>
+        <v>43.57272720336914</v>
       </c>
       <c r="C12" t="n">
         <v>58.72000122070312</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.01972198486328</v>
+        <v>45.01971435546875</v>
       </c>
       <c r="C13" t="n">
         <v>60.66999816894531</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>43.30878829956055</v>
+        <v>43.30879592895508</v>
       </c>
       <c r="C14" t="n">
         <v>58.22000122070312</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.30453872680664</v>
+        <v>42.30454254150391</v>
       </c>
       <c r="C15" t="n">
         <v>56.86999893188477</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.95491027832031</v>
+        <v>41.95492553710938</v>
       </c>
       <c r="C16" t="n">
         <v>56.40000152587891</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>48.46758651733398</v>
+        <v>48.46756362915039</v>
       </c>
       <c r="C18" t="n">
         <v>64.98000335693359</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.63322830200195</v>
+        <v>45.63321685791016</v>
       </c>
       <c r="C19" t="n">
         <v>61.18000030517578</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.77035140991211</v>
+        <v>43.77034759521484</v>
       </c>
       <c r="C20" t="n">
         <v>58.54000091552734</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>43.83015441894531</v>
+        <v>43.83016586303711</v>
       </c>
       <c r="C21" t="n">
         <v>58.61999893188477</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>44.39091110229492</v>
+        <v>44.39092636108398</v>
       </c>
       <c r="C22" t="n">
         <v>59.36999893188477</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>45.68533325195312</v>
+        <v>45.68533706665039</v>
       </c>
       <c r="C23" t="n">
         <v>60.95000076293945</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.20871734619141</v>
+        <v>44.20869827270508</v>
       </c>
       <c r="C24" t="n">
         <v>58.97999954223633</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>36.95349502563477</v>
+        <v>36.95346069335938</v>
       </c>
       <c r="C26" t="n">
         <v>49.13000106811523</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>31.81624984741211</v>
+        <v>31.81625175476074</v>
       </c>
       <c r="C27" t="n">
         <v>42.29999923706055</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.44394302368164</v>
+        <v>28.44392776489258</v>
       </c>
       <c r="C31" t="n">
         <v>37.66999816894531</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.15057754516602</v>
+        <v>28.15058326721191</v>
       </c>
       <c r="C32" t="n">
         <v>37.11999893188477</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>30.09200477600098</v>
+        <v>30.09202003479004</v>
       </c>
       <c r="C33" t="n">
         <v>39.68000030517578</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.86894035339355</v>
+        <v>26.86895751953125</v>
       </c>
       <c r="C34" t="n">
         <v>35.43000030517578</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.96159553527832</v>
+        <v>20.96159172058105</v>
       </c>
       <c r="C35" t="n">
         <v>27.5</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.7678050994873</v>
+        <v>17.76780700683594</v>
       </c>
       <c r="C36" t="n">
         <v>23.30999946594238</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.13955211639404</v>
+        <v>14.13954925537109</v>
       </c>
       <c r="C37" t="n">
         <v>18.54999923706055</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.271816253662109</v>
+        <v>9.271821022033691</v>
       </c>
       <c r="C39" t="n">
         <v>12.0600004196167</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.47884750366211</v>
+        <v>10.47884845733643</v>
       </c>
       <c r="C40" t="n">
         <v>13.63000011444092</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>19.6488094329834</v>
+        <v>19.64881706237793</v>
       </c>
       <c r="C41" t="n">
         <v>25.21999931335449</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.36054801940918</v>
+        <v>19.36054039001465</v>
       </c>
       <c r="C42" t="n">
         <v>24.85000038146973</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.2430248260498</v>
+        <v>18.24302101135254</v>
       </c>
       <c r="C43" t="n">
         <v>23.23999977111816</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>26.54815483093262</v>
+        <v>26.54814910888672</v>
       </c>
       <c r="C45" t="n">
         <v>33.81999969482422</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>26.75262451171875</v>
+        <v>26.75263023376465</v>
       </c>
       <c r="C46" t="n">
         <v>33.90000152587891</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.49444580078125</v>
+        <v>27.49442863464355</v>
       </c>
       <c r="C47" t="n">
         <v>34.84000015258789</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>33.01069259643555</v>
+        <v>33.01068496704102</v>
       </c>
       <c r="C48" t="n">
         <v>41.83000183105469</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>31.97688293457031</v>
+        <v>31.97687911987305</v>
       </c>
       <c r="C49" t="n">
         <v>40.52000045776367</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>29.8493709564209</v>
+        <v>29.84938812255859</v>
       </c>
       <c r="C50" t="n">
         <v>37.65999984741211</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>30.26945877075195</v>
+        <v>30.26946067810059</v>
       </c>
       <c r="C51" t="n">
         <v>38.18999862670898</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.84529113769531</v>
+        <v>32.84527969360352</v>
       </c>
       <c r="C52" t="n">
         <v>41.2599983215332</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.71411514282227</v>
+        <v>36.71410751342773</v>
       </c>
       <c r="C53" t="n">
         <v>46.11999893188477</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.7387752532959</v>
+        <v>31.73876571655273</v>
       </c>
       <c r="C54" t="n">
         <v>39.86999893188477</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.74595260620117</v>
+        <v>31.74596214294434</v>
       </c>
       <c r="C55" t="n">
         <v>39.70000076293945</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>35.69622802734375</v>
+        <v>35.69620895385742</v>
       </c>
       <c r="C56" t="n">
         <v>44.63999938964844</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>31.88189888000488</v>
+        <v>31.88191223144531</v>
       </c>
       <c r="C57" t="n">
         <v>39.86999893188477</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>33.6091423034668</v>
+        <v>33.60913848876953</v>
       </c>
       <c r="C58" t="n">
         <v>42.02999877929688</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.30996704101562</v>
+        <v>33.30998229980469</v>
       </c>
       <c r="C59" t="n">
         <v>41.45999908447266</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>34.72399520874023</v>
+        <v>34.72399139404297</v>
       </c>
       <c r="C60" t="n">
         <v>43.22000122070312</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.48296356201172</v>
+        <v>34.48296737670898</v>
       </c>
       <c r="C61" t="n">
         <v>42.91999816894531</v>
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.99586868286133</v>
+        <v>34.99587249755859</v>
       </c>
       <c r="C62" t="n">
         <v>43.38000106811523</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>35.14914321899414</v>
+        <v>35.14915466308594</v>
       </c>
       <c r="C63" t="n">
         <v>43.56999969482422</v>
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.46410751342773</v>
+        <v>36.464111328125</v>
       </c>
       <c r="C64" t="n">
         <v>45.20000076293945</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.75174713134766</v>
+        <v>39.75175857543945</v>
       </c>
       <c r="C65" t="n">
         <v>49.08000183105469</v>
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>42.02563858032227</v>
+        <v>42.025634765625</v>
       </c>
       <c r="C67" t="n">
         <v>51.70000076293945</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.6762809753418</v>
+        <v>40.67626190185547</v>
       </c>
       <c r="C68" t="n">
         <v>50.04000091552734</v>
@@ -1917,11 +1929,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.40801620483398</v>
+        <v>40.40800857543945</v>
       </c>
       <c r="C69" t="n">
         <v>49.70999908447266</v>
@@ -1946,11 +1958,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.49809646606445</v>
+        <v>36.49808502197266</v>
       </c>
       <c r="C70" t="n">
         <v>44.90000152587891</v>
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.3189811706543</v>
+        <v>41.31897354125977</v>
       </c>
       <c r="C71" t="n">
         <v>50.61999893188477</v>
@@ -2004,11 +2016,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>39.21303558349609</v>
+        <v>39.21304702758789</v>
       </c>
       <c r="C72" t="n">
         <v>48.04000091552734</v>
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>38.50289154052734</v>
+        <v>38.50288772583008</v>
       </c>
       <c r="C73" t="n">
         <v>47.16999816894531</v>
@@ -2062,7 +2074,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>43.33307647705078</v>
+        <v>43.33306884765625</v>
       </c>
       <c r="C75" t="n">
         <v>52.88999938964844</v>
@@ -2120,7 +2132,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.50105667114258</v>
+        <v>49.50106048583984</v>
       </c>
       <c r="C77" t="n">
         <v>60.20999908447266</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.90008544921875</v>
+        <v>45.90008163452148</v>
       </c>
       <c r="C78" t="n">
         <v>55.83000183105469</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>47.85677719116211</v>
+        <v>47.85676574707031</v>
       </c>
       <c r="C79" t="n">
         <v>58.20999908447266</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>47.60695266723633</v>
+        <v>47.60694885253906</v>
       </c>
       <c r="C80" t="n">
         <v>57.70999908447266</v>
@@ -2265,11 +2277,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>48.09365844726562</v>
+        <v>48.09365463256836</v>
       </c>
       <c r="C81" t="n">
         <v>58.29999923706055</v>
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>46.90575408935547</v>
+        <v>46.90576171875</v>
       </c>
       <c r="C82" t="n">
         <v>56.86000061035156</v>
@@ -2323,11 +2335,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>46.33362197875977</v>
+        <v>46.3336181640625</v>
       </c>
       <c r="C83" t="n">
         <v>55.97000122070312</v>
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>46.27566909790039</v>
+        <v>46.27568435668945</v>
       </c>
       <c r="C84" t="n">
         <v>55.90000152587891</v>
@@ -2381,11 +2393,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>47.58365249633789</v>
+        <v>47.58365631103516</v>
       </c>
       <c r="C85" t="n">
         <v>57.47999954223633</v>
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.85465240478516</v>
+        <v>48.85466384887695</v>
       </c>
       <c r="C86" t="n">
         <v>58.81000137329102</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>51.62926864624023</v>
+        <v>51.62925338745117</v>
       </c>
       <c r="C87" t="n">
         <v>62.15000152587891</v>
@@ -2468,11 +2480,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>56.04037094116211</v>
+        <v>56.04038238525391</v>
       </c>
       <c r="C88" t="n">
         <v>67.45999908447266</v>
@@ -2497,11 +2509,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>56.99810791015625</v>
+        <v>56.99810028076172</v>
       </c>
       <c r="C89" t="n">
         <v>68.41000366210938</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>63.08032608032227</v>
+        <v>63.08036804199219</v>
       </c>
       <c r="C90" t="n">
         <v>75.70999908447266</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>62.28881454467773</v>
+        <v>62.28879928588867</v>
       </c>
       <c r="C91" t="n">
         <v>74.76000213623047</v>
@@ -2584,11 +2596,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>61.65142059326172</v>
+        <v>61.65141677856445</v>
       </c>
       <c r="C92" t="n">
         <v>73.76999664306641</v>
@@ -2613,11 +2625,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>60.09698486328125</v>
+        <v>60.09699249267578</v>
       </c>
       <c r="C93" t="n">
         <v>71.91000366210938</v>
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>63.11394119262695</v>
+        <v>63.11392593383789</v>
       </c>
       <c r="C94" t="n">
         <v>75.51999664306641</v>
@@ -2671,11 +2683,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>68.57002258300781</v>
+        <v>68.56999206542969</v>
       </c>
       <c r="C95" t="n">
         <v>81.80000305175781</v>
@@ -2696,11 +2708,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>71.92307281494141</v>
+        <v>71.92306518554688</v>
       </c>
       <c r="C96" t="n">
         <v>85.80000305175781</v>
@@ -2721,11 +2733,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>76.05569458007812</v>
+        <v>76.05571746826172</v>
       </c>
       <c r="C97" t="n">
         <v>90.73000335693359</v>
@@ -2746,7 +2758,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2771,11 +2783,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>76.71421051025391</v>
+        <v>76.71420288085938</v>
       </c>
       <c r="C99" t="n">
         <v>91.27999877929688</v>
@@ -2800,11 +2812,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>75.66365814208984</v>
+        <v>75.66366577148438</v>
       </c>
       <c r="C100" t="n">
         <v>90.02999877929688</v>
@@ -2829,11 +2841,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>73.66442108154297</v>
+        <v>73.66438293457031</v>
       </c>
       <c r="C101" t="n">
         <v>87.43000030517578</v>
@@ -2858,11 +2870,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>77.09358215332031</v>
+        <v>77.09355926513672</v>
       </c>
       <c r="C102" t="n">
         <v>91.5</v>
@@ -2887,11 +2899,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>79.9329833984375</v>
+        <v>79.93299102783203</v>
       </c>
       <c r="C103" t="n">
         <v>94.87000274658203</v>
@@ -2916,11 +2928,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.34909057617188</v>
+        <v>74.34906768798828</v>
       </c>
       <c r="C104" t="n">
         <v>88</v>
@@ -2945,11 +2957,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>75.65858459472656</v>
+        <v>75.65863037109375</v>
       </c>
       <c r="C105" t="n">
         <v>89.55000305175781</v>
@@ -2974,11 +2986,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>73.96041107177734</v>
+        <v>73.96040344238281</v>
       </c>
       <c r="C106" t="n">
         <v>87.54000091552734</v>
@@ -3003,7 +3015,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3032,11 +3044,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>78.31600952148438</v>
+        <v>78.31599426269531</v>
       </c>
       <c r="C108" t="n">
         <v>92.41999816894531</v>
@@ -3061,11 +3073,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>78.84140014648438</v>
+        <v>78.84138488769531</v>
       </c>
       <c r="C109" t="n">
         <v>93.04000091552734</v>
@@ -3090,11 +3102,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>68.57729339599609</v>
+        <v>68.57727813720703</v>
       </c>
       <c r="C110" t="n">
         <v>80.69000244140625</v>
@@ -3119,11 +3131,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>69.34217834472656</v>
+        <v>69.34214782714844</v>
       </c>
       <c r="C111" t="n">
         <v>81.58999633789062</v>
@@ -3148,11 +3160,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.61495971679688</v>
+        <v>66.61498260498047</v>
       </c>
       <c r="C112" t="n">
         <v>78.12000274658203</v>
@@ -3177,11 +3189,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>66.04364776611328</v>
+        <v>66.04366302490234</v>
       </c>
       <c r="C113" t="n">
         <v>77.44999694824219</v>
@@ -3206,11 +3218,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>67.97935485839844</v>
+        <v>67.97930908203125</v>
       </c>
       <c r="C114" t="n">
         <v>79.72000122070312</v>
@@ -3235,11 +3247,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>66.52185821533203</v>
+        <v>66.52186584472656</v>
       </c>
       <c r="C115" t="n">
         <v>77.72000122070312</v>
@@ -3264,7 +3276,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3293,11 +3305,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>65.66592407226562</v>
+        <v>65.66593170166016</v>
       </c>
       <c r="C117" t="n">
         <v>76.72000122070312</v>
@@ -3322,11 +3334,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>63.44912719726562</v>
+        <v>63.44909286499023</v>
       </c>
       <c r="C118" t="n">
         <v>74.12999725341797</v>
@@ -3351,11 +3363,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>62.94182205200195</v>
+        <v>62.94177627563477</v>
       </c>
       <c r="C119" t="n">
         <v>73.26000213623047</v>
@@ -3380,11 +3392,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>61.54994583129883</v>
+        <v>61.54994201660156</v>
       </c>
       <c r="C120" t="n">
         <v>71.63999938964844</v>
@@ -3409,11 +3421,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>59.75431060791016</v>
+        <v>59.75429916381836</v>
       </c>
       <c r="C121" t="n">
         <v>69.55000305175781</v>
@@ -3438,11 +3450,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>46.16603088378906</v>
+        <v>46.16603469848633</v>
       </c>
       <c r="C122" t="n">
         <v>53.5</v>
@@ -3467,7 +3479,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3496,7 +3508,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3525,11 +3537,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>56.73396301269531</v>
+        <v>56.73399353027344</v>
       </c>
       <c r="C125" t="n">
         <v>65.43000030517578</v>
@@ -3554,11 +3566,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.0201301574707</v>
+        <v>57.02012634277344</v>
       </c>
       <c r="C126" t="n">
         <v>65.76000213623047</v>
@@ -3583,11 +3595,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>52.94985580444336</v>
+        <v>52.94984436035156</v>
       </c>
       <c r="C127" t="n">
         <v>60.7599983215332</v>
@@ -3612,11 +3624,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.17425537109375</v>
+        <v>56.17427062988281</v>
       </c>
       <c r="C128" t="n">
         <v>64.45999908447266</v>
@@ -3641,11 +3653,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>57.1502799987793</v>
+        <v>57.15028381347656</v>
       </c>
       <c r="C129" t="n">
         <v>65.58000183105469</v>
@@ -3670,7 +3682,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3699,11 +3711,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>58.17360305786133</v>
+        <v>58.173583984375</v>
       </c>
       <c r="C131" t="n">
         <v>66.41999816894531</v>
@@ -3728,11 +3740,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.09582901000977</v>
+        <v>63.09584045410156</v>
       </c>
       <c r="C132" t="n">
         <v>72.04000091552734</v>
@@ -3757,11 +3769,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>64.88255310058594</v>
+        <v>64.88253784179688</v>
       </c>
       <c r="C133" t="n">
         <v>74.08000183105469</v>
@@ -3786,11 +3798,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.18231201171875</v>
+        <v>67.18229675292969</v>
       </c>
       <c r="C134" t="n">
         <v>76.37999725341797</v>
@@ -3815,11 +3827,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.41915130615234</v>
+        <v>70.419189453125</v>
       </c>
       <c r="C135" t="n">
         <v>80.05999755859375</v>
@@ -3844,11 +3856,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>69.58356475830078</v>
+        <v>69.58355712890625</v>
       </c>
       <c r="C136" t="n">
         <v>79.11000061035156</v>
@@ -3873,11 +3885,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>69.99290466308594</v>
+        <v>69.99288940429688</v>
       </c>
       <c r="C137" t="n">
         <v>79.25</v>
@@ -3902,11 +3914,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>67.95272064208984</v>
+        <v>67.95272827148438</v>
       </c>
       <c r="C138" t="n">
         <v>76.94000244140625</v>
@@ -3931,11 +3943,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>74.40004730224609</v>
+        <v>74.40003204345703</v>
       </c>
       <c r="C139" t="n">
         <v>84.23999786376953</v>
@@ -3960,11 +3972,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>75.55851745605469</v>
+        <v>75.55854034423828</v>
       </c>
       <c r="C140" t="n">
         <v>85.23000335693359</v>
@@ -3989,11 +4001,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>76.32977294921875</v>
+        <v>76.32980346679688</v>
       </c>
       <c r="C141" t="n">
         <v>86.09999847412109</v>
@@ -4018,11 +4030,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>80.19503021240234</v>
+        <v>80.19501495361328</v>
       </c>
       <c r="C142" t="n">
         <v>90.45999908447266</v>
@@ -4047,7 +4059,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4076,11 +4088,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>86.95674896240234</v>
+        <v>86.95675659179688</v>
       </c>
       <c r="C144" t="n">
         <v>97.70999908447266</v>
@@ -4105,11 +4117,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>88.38067626953125</v>
+        <v>88.38064575195312</v>
       </c>
       <c r="C145" t="n">
         <v>99.30999755859375</v>
@@ -4134,11 +4146,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>88.77289581298828</v>
+        <v>88.77285766601562</v>
       </c>
       <c r="C146" t="n">
         <v>99.40000152587891</v>
@@ -4163,11 +4175,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>87.08492279052734</v>
+        <v>87.08494567871094</v>
       </c>
       <c r="C147" t="n">
         <v>97.51000213623047</v>
@@ -4192,11 +4204,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>83.30718994140625</v>
+        <v>83.30717468261719</v>
       </c>
       <c r="C148" t="n">
         <v>93.27999877929688</v>
@@ -4221,11 +4233,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>88.52346801757812</v>
+        <v>88.52346038818359</v>
       </c>
       <c r="C149" t="n">
         <v>98.75</v>
@@ -4250,7 +4262,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4279,11 +4291,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>87.85112762451172</v>
+        <v>87.85111236572266</v>
       </c>
       <c r="C151" t="n">
         <v>98</v>
@@ -4308,11 +4320,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>89.53397369384766</v>
+        <v>89.53401184082031</v>
       </c>
       <c r="C152" t="n">
         <v>99.51999664306641</v>
@@ -4337,11 +4349,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>95.34580993652344</v>
+        <v>95.34580230712891</v>
       </c>
       <c r="C153" t="n">
         <v>105.9800033569336</v>
@@ -4366,11 +4378,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>95.80461883544922</v>
+        <v>95.80463409423828</v>
       </c>
       <c r="C154" t="n">
         <v>106.4899978637695</v>
@@ -4395,7 +4407,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4424,11 +4436,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>101.3691787719727</v>
+        <v>101.3691864013672</v>
       </c>
       <c r="C156" t="n">
         <v>112.2699966430664</v>
@@ -4453,11 +4465,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>86.06496429443359</v>
+        <v>86.06492614746094</v>
       </c>
       <c r="C157" t="n">
         <v>95.31999969482422</v>
@@ -4482,11 +4494,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>93.10790252685547</v>
+        <v>93.10788726806641</v>
       </c>
       <c r="C158" t="n">
         <v>102.6999969482422</v>
@@ -4511,7 +4523,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4540,11 +4552,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>99.09146881103516</v>
+        <v>99.09147644042969</v>
       </c>
       <c r="C160" t="n">
         <v>109.3000030517578</v>
@@ -4569,11 +4581,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>106.6570510864258</v>
+        <v>106.6570358276367</v>
       </c>
       <c r="C161" t="n">
         <v>117.2300033569336</v>
@@ -4598,11 +4610,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>104.3643341064453</v>
+        <v>104.3643264770508</v>
       </c>
       <c r="C162" t="n">
         <v>114.7099990844727</v>
@@ -4627,11 +4639,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>112.3069610595703</v>
+        <v>112.3069458007812</v>
       </c>
       <c r="C163" t="n">
         <v>123.4400024414062</v>
@@ -4656,11 +4668,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>113.506950378418</v>
+        <v>113.5069351196289</v>
       </c>
       <c r="C164" t="n">
         <v>124.370002746582</v>
@@ -4685,11 +4697,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>109.8563385009766</v>
+        <v>109.8563003540039</v>
       </c>
       <c r="C165" t="n">
         <v>120.370002746582</v>
@@ -4714,11 +4726,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>107.9488677978516</v>
+        <v>107.9488525390625</v>
       </c>
       <c r="C166" t="n">
         <v>118.2799987792969</v>
@@ -4743,11 +4755,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>107.4455871582031</v>
+        <v>107.4455795288086</v>
       </c>
       <c r="C167" t="n">
         <v>117.2799987792969</v>
@@ -4772,11 +4784,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>110.0474624633789</v>
+        <v>110.0474243164062</v>
       </c>
       <c r="C168" t="n">
         <v>120.120002746582</v>
@@ -4801,11 +4813,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>114.0509796142578</v>
+        <v>114.0510025024414</v>
       </c>
       <c r="C169" t="n">
         <v>124.4899978637695</v>
@@ -4830,11 +4842,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>119.3922500610352</v>
+        <v>119.3922576904297</v>
       </c>
       <c r="C170" t="n">
         <v>129.8699951171875</v>
@@ -4859,11 +4871,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>101.0609970092773</v>
+        <v>101.0609893798828</v>
       </c>
       <c r="C171" t="n">
         <v>109.9300003051758</v>
@@ -4888,11 +4900,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>78.70308685302734</v>
+        <v>78.70307159423828</v>
       </c>
       <c r="C172" t="n">
         <v>85.61000061035156</v>
@@ -4917,7 +4929,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4946,11 +4958,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>87.8853759765625</v>
+        <v>87.88536071777344</v>
       </c>
       <c r="C174" t="n">
         <v>95.06999969482422</v>
@@ -4975,7 +4987,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5004,7 +5016,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5033,7 +5045,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5062,11 +5074,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>93.09439849853516</v>
+        <v>93.09438323974609</v>
       </c>
       <c r="C178" t="n">
         <v>100.25</v>
@@ -5091,11 +5103,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>85.08138275146484</v>
+        <v>85.08137512207031</v>
       </c>
       <c r="C179" t="n">
         <v>91.23999786376953</v>
@@ -5120,11 +5132,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>110.5852737426758</v>
+        <v>110.5852890014648</v>
       </c>
       <c r="C180" t="n">
         <v>118.5899963378906</v>
@@ -5149,11 +5161,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>112.7486801147461</v>
+        <v>112.7486877441406</v>
       </c>
       <c r="C181" t="n">
         <v>120.9100036621094</v>
@@ -5178,11 +5190,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>108.792724609375</v>
+        <v>108.7926940917969</v>
       </c>
       <c r="C182" t="n">
         <v>116.2600021362305</v>
@@ -5207,11 +5219,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>126.5723037719727</v>
+        <v>126.5723419189453</v>
       </c>
       <c r="C183" t="n">
         <v>135.2599945068359</v>
@@ -5236,7 +5248,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5265,7 +5277,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5294,11 +5306,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>150.2953796386719</v>
+        <v>150.2953643798828</v>
       </c>
       <c r="C186" t="n">
         <v>160.1300048828125</v>
@@ -5323,11 +5335,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>155.0821228027344</v>
+        <v>155.0820922851562</v>
       </c>
       <c r="C187" t="n">
         <v>165.2299957275391</v>
@@ -5352,11 +5364,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>160.4742279052734</v>
+        <v>160.4742736816406</v>
       </c>
       <c r="C188" t="n">
         <v>170.5299987792969</v>
@@ -5381,11 +5393,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>156.1737365722656</v>
+        <v>156.1737670898438</v>
       </c>
       <c r="C189" t="n">
         <v>165.9600067138672</v>
@@ -5410,11 +5422,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>157.6511535644531</v>
+        <v>157.6511077880859</v>
       </c>
       <c r="C190" t="n">
         <v>167.5299987792969</v>
@@ -5439,11 +5451,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>163.9391174316406</v>
+        <v>163.9391632080078</v>
       </c>
       <c r="C191" t="n">
         <v>173.7799987792969</v>
@@ -5468,11 +5480,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>143.6755218505859</v>
+        <v>143.6755065917969</v>
       </c>
       <c r="C192" t="n">
         <v>152.3000030517578</v>
@@ -5497,11 +5509,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>154.3356170654297</v>
+        <v>154.3356323242188</v>
       </c>
       <c r="C193" t="n">
         <v>163.6000061035156</v>
@@ -5526,11 +5538,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>170.0628509521484</v>
+        <v>170.0628814697266</v>
       </c>
       <c r="C194" t="n">
         <v>179.8200073242188</v>
@@ -5555,11 +5567,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>183.9841156005859</v>
+        <v>183.984130859375</v>
       </c>
       <c r="C195" t="n">
         <v>194.5399932861328</v>
@@ -5584,11 +5596,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>176.8532867431641</v>
+        <v>176.8533020019531</v>
       </c>
       <c r="C196" t="n">
         <v>187</v>
@@ -5613,11 +5625,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>165.6991577148438</v>
+        <v>165.6991729736328</v>
       </c>
       <c r="C197" t="n">
         <v>174.7100067138672</v>
@@ -5642,11 +5654,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>160.1129455566406</v>
+        <v>160.1129302978516</v>
       </c>
       <c r="C198" t="n">
         <v>168.8200073242188</v>
@@ -5671,11 +5683,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>131.9625244140625</v>
+        <v>131.9625396728516</v>
       </c>
       <c r="C199" t="n">
         <v>138.6199951171875</v>
@@ -5700,11 +5712,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>146.6229553222656</v>
+        <v>146.6229248046875</v>
       </c>
       <c r="C200" t="n">
         <v>154.0200042724609</v>
@@ -5729,7 +5741,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5758,11 +5770,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>128.4307098388672</v>
+        <v>128.4307403564453</v>
       </c>
       <c r="C202" t="n">
         <v>134.9100036621094</v>
@@ -5787,11 +5799,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>141.8599090576172</v>
+        <v>141.8598785400391</v>
       </c>
       <c r="C203" t="n">
         <v>148.4499969482422</v>
@@ -5816,7 +5828,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5845,11 +5857,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>141.1909790039062</v>
+        <v>141.1909942626953</v>
       </c>
       <c r="C205" t="n">
         <v>147.75</v>
@@ -5874,11 +5886,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>167.7438201904297</v>
+        <v>167.7437896728516</v>
       </c>
       <c r="C206" t="n">
         <v>174.9299926757812</v>
@@ -5903,11 +5915,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>166.8424224853516</v>
+        <v>166.8424377441406</v>
       </c>
       <c r="C207" t="n">
         <v>173.9900054931641</v>
@@ -5932,11 +5944,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>158.1738128662109</v>
+        <v>158.1737823486328</v>
       </c>
       <c r="C208" t="n">
         <v>164.9499969482422</v>
@@ -5961,11 +5973,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>155.2852325439453</v>
+        <v>155.2852478027344</v>
       </c>
       <c r="C209" t="n">
         <v>161.3399963378906</v>
@@ -5990,11 +6002,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>152.6095886230469</v>
+        <v>152.6095733642578</v>
       </c>
       <c r="C210" t="n">
         <v>158.5599975585938</v>
@@ -6019,7 +6031,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6048,11 +6060,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>163.0997009277344</v>
+        <v>163.0996704101562</v>
       </c>
       <c r="C212" t="n">
         <v>168.8800048828125</v>
@@ -6077,11 +6089,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>152.5824279785156</v>
+        <v>152.5824127197266</v>
       </c>
       <c r="C213" t="n">
         <v>157.9900054931641</v>
@@ -6106,11 +6118,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>144.0835876464844</v>
+        <v>144.0836181640625</v>
       </c>
       <c r="C214" t="n">
         <v>149.1900024414062</v>
@@ -6135,7 +6147,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6164,11 +6176,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>165.6026306152344</v>
+        <v>165.6026153564453</v>
       </c>
       <c r="C216" t="n">
         <v>170.7700042724609</v>
@@ -6193,11 +6205,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>181.6712188720703</v>
+        <v>181.6712341308594</v>
       </c>
       <c r="C217" t="n">
         <v>187.3399963378906</v>
@@ -6222,11 +6234,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>195.2946472167969</v>
+        <v>195.2946624755859</v>
       </c>
       <c r="C218" t="n">
         <v>200.7400054931641</v>
@@ -6251,11 +6263,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>213.4679260253906</v>
+        <v>213.4679107666016</v>
       </c>
       <c r="C219" t="n">
         <v>219.4199981689453</v>
@@ -6280,7 +6292,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6309,11 +6321,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>228.3870086669922</v>
+        <v>228.3870239257812</v>
       </c>
       <c r="C221" t="n">
         <v>234.0299987792969</v>
@@ -6338,11 +6350,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>234.2130889892578</v>
+        <v>234.2130584716797</v>
       </c>
       <c r="C222" t="n">
         <v>240</v>
@@ -6367,7 +6379,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6396,11 +6408,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>247.6741943359375</v>
+        <v>247.6741790771484</v>
       </c>
       <c r="C224" t="n">
         <v>253.0399932861328</v>
@@ -6425,11 +6437,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>253.1652221679688</v>
+        <v>253.1652069091797</v>
       </c>
       <c r="C225" t="n">
         <v>258.6499938964844</v>
@@ -6454,11 +6466,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>265.4490661621094</v>
+        <v>265.4491577148438</v>
       </c>
       <c r="C226" t="n">
         <v>271.2000122070312</v>
@@ -6483,11 +6495,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>265.0436401367188</v>
+        <v>265.0435791015625</v>
       </c>
       <c r="C227" t="n">
         <v>270.0799865722656</v>
@@ -6512,11 +6524,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>298.9983520507812</v>
+        <v>298.9984130859375</v>
       </c>
       <c r="C228" t="n">
         <v>304.6799926757812</v>
@@ -6541,11 +6553,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>291.2555236816406</v>
+        <v>291.2555541992188</v>
       </c>
       <c r="C229" t="n">
         <v>296.7900085449219</v>
@@ -6570,7 +6582,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6599,11 +6611,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>296.0421142578125</v>
+        <v>296.0421447753906</v>
       </c>
       <c r="C231" t="n">
         <v>300.9599914550781</v>
@@ -6628,11 +6640,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>264.6535949707031</v>
+        <v>264.6536254882812</v>
       </c>
       <c r="C232" t="n">
         <v>269.0499877929688</v>
@@ -6657,7 +6669,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6686,11 +6698,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>290.2052917480469</v>
+        <v>290.205322265625</v>
       </c>
       <c r="C234" t="n">
         <v>294.0499877929688</v>
@@ -6715,7 +6727,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6744,11 +6756,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>296.1423645019531</v>
+        <v>296.142333984375</v>
       </c>
       <c r="C236" t="n">
         <v>299.3099975585938</v>
@@ -6773,11 +6785,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>327.7739868164062</v>
+        <v>327.7740173339844</v>
       </c>
       <c r="C237" t="n">
         <v>331.2799987792969</v>
@@ -6802,7 +6814,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6831,7 +6843,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6860,7 +6872,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6889,7 +6901,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6918,7 +6930,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6947,7 +6959,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6976,7 +6988,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7005,7 +7017,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7034,7 +7046,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7063,7 +7075,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7092,7 +7104,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7121,7 +7133,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7150,32 +7162,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>301.9599914550781</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>301.9599914550781</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>49281500</v>
+        <v>53233100</v>
       </c>
       <c r="E250" t="n">
         <v>16.47</v>
       </c>
       <c r="F250" t="n">
-        <v>18.33393997905756</v>
+        <v>18.5585916006138</v>
       </c>
       <c r="G250" t="n">
         <v>675309833</v>
       </c>
       <c r="H250" t="n">
-        <v>203916551402.2102</v>
+        <v>206415206027.8385</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07297613271980892</v>
+        <v>0.07882766901751896</v>
       </c>
     </row>
   </sheetData>
@@ -7207,75 +7219,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40058</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7311,13 +7323,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7353,13 +7365,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7395,13 +7407,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40058</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7437,13 +7449,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7479,13 +7491,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7512,7 +7524,7 @@
       <c r="I7" t="n">
         <v>1.53</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7558,7 +7570,7 @@
       <c r="I8" t="n">
         <v>1.95</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I9" t="n">
         <v>2.7</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I10" t="n">
         <v>3.07</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I11" t="n">
         <v>3.35</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I12" t="n">
         <v>3.59</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I13" t="n">
         <v>3.85</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="K13" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I14" t="n">
         <v>3.98</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I15" t="n">
         <v>4.11</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I16" t="n">
         <v>4.21</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="K16" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I17" t="n">
         <v>4.26</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K17" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I18" t="n">
         <v>4.32</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K18" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I19" t="n">
         <v>3.87</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I20" t="n">
         <v>3.957323688969258</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K20" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41484</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I21" t="n">
         <v>4.088089413672996</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K21" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I22" t="n">
         <v>4.261734187030997</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K22" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I23" t="n">
         <v>4.902836115405654</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K23" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I24" t="n">
         <v>5.087593026248953</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K24" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I25" t="n">
         <v>5.252006885666199</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K25" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I26" t="n">
         <v>5.388362112308197</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I27" t="n">
         <v>5.577260183933541</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K27" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I28" t="n">
         <v>5.725893171608764</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K28" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I29" t="n">
         <v>5.734810329837238</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K29" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I30" t="n">
         <v>5.574810329837238</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K30" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I31" t="n">
         <v>5.074810329837238</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K31" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I32" t="n">
         <v>5.064885942764826</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I33" t="n">
         <v>5.710789200415368</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="K33" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I34" t="n">
         <v>5.670789200415368</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K34" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I35" t="n">
         <v>5.660789200415368</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K35" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I36" t="n">
         <v>5.52</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I37" t="n">
         <v>4.89</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="K37" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I38" t="n">
         <v>5.19</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="K38" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I39" t="n">
         <v>2.9</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K39" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I40" t="n">
         <v>3.42</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I41" t="n">
         <v>3.79</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="K41" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I42" t="n">
         <v>4.17</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="K42" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I43" t="n">
         <v>7.9</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K43" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I44" t="n">
         <v>7.84</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="K44" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I45" t="n">
         <v>8.07</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="K45" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I46" t="n">
         <v>8.27</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="K46" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I47" t="n">
         <v>7.98</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K47" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I48" t="n">
         <v>6.59</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="K48" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I49" t="n">
         <v>4.81</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="K49" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I50" t="n">
         <v>4.029999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="K50" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I51" t="n">
         <v>3.76</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K51" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I52" t="n">
         <v>6.09</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="K52" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I53" t="n">
         <v>8.6</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="K53" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I54" t="n">
         <v>9.57</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="K54" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I55" t="n">
         <v>10.02</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I56" t="n">
         <v>10.01</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K56" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I57" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="K57" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I58" t="n">
         <v>9.98</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="K58" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I59" t="n">
         <v>9.850000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I60" t="n">
         <v>9.52</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="K60" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I61" t="n">
         <v>9.84</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K61" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I62" t="n">
         <v>10.67</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="K62" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I63" t="n">
         <v>11.21</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="K63" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I64" t="n">
         <v>12.14</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="K64" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I65" t="n">
         <v>13.4</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="K65" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I66" t="n">
         <v>13.59</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="K66" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I67" t="n">
         <v>14.01</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="K67" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I68" t="n">
         <v>14.32</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="K68" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I69" t="n">
         <v>14.25</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="K69" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I70" t="n">
         <v>14.9</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="K70" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I71" t="n">
         <v>15.38</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K71" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I72" t="n">
         <v>16.02</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K72" t="n">
@@ -10515,13 +10527,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10548,7 +10560,7 @@
       <c r="I73" t="n">
         <v>16.47</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K73" t="n">
@@ -10585,52 +10597,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40017</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40058</v>
       </c>
       <c r="C2" t="n">
@@ -10659,10 +10671,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40108</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="C3" t="n">
@@ -10691,10 +10703,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10723,10 +10735,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C5" t="n">
@@ -10755,10 +10767,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10787,10 +10799,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40479</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10819,10 +10831,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40596</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10883,10 +10895,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C10" t="n">
@@ -10915,10 +10927,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C11" t="n">
@@ -10947,10 +10959,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40961</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10979,10 +10991,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="C13" t="n">
@@ -11011,10 +11023,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -11043,10 +11055,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C15" t="n">
@@ -11075,10 +11087,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11107,10 +11119,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41382</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41393</v>
       </c>
       <c r="C17" t="n">
@@ -11139,10 +11151,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41478</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41484</v>
       </c>
       <c r="C18" t="n">
@@ -11171,10 +11183,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41570</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C19" t="n">
@@ -11203,10 +11215,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C20" t="n">
@@ -11235,10 +11247,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C21" t="n">
@@ -11267,10 +11279,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C22" t="n">
@@ -11299,10 +11311,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="C23" t="n">
@@ -11331,10 +11343,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C24" t="n">
@@ -11363,10 +11375,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C25" t="n">
@@ -11395,10 +11407,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42209</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11427,10 +11439,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11459,10 +11471,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42408</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11491,10 +11503,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11523,10 +11535,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="C30" t="n">
@@ -11555,10 +11567,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42661</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C31" t="n">
@@ -11587,10 +11599,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42774</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C32" t="n">
@@ -11619,10 +11631,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11651,10 +11663,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C34" t="n">
@@ -11683,10 +11695,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43026</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="C35" t="n">
@@ -11715,10 +11727,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43137</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C36" t="n">
@@ -11747,10 +11759,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43208</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11779,10 +11791,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43299</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="C38" t="n">
@@ -11811,10 +11823,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43388</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="C39" t="n">
@@ -11843,10 +11855,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43500</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C40" t="n">
@@ -11875,10 +11887,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43570</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="C41" t="n">
@@ -11907,10 +11919,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43661</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="C42" t="n">
@@ -11939,10 +11951,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43752</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="C43" t="n">
@@ -11971,10 +11983,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43860</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C44" t="n">
@@ -12003,10 +12015,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43941</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="C45" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="C46" t="n">
@@ -12067,10 +12079,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C47" t="n">
@@ -12099,10 +12111,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44230</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C48" t="n">
@@ -12131,10 +12143,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44305</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="C49" t="n">
@@ -12163,10 +12175,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44396</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="C50" t="n">
@@ -12195,10 +12207,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44487</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="C51" t="n">
@@ -12227,10 +12239,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44595</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -12259,10 +12271,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44669</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C53" t="n">
@@ -12291,10 +12303,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44760</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="C54" t="n">
@@ -12323,10 +12335,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44846</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="C55" t="n">
@@ -12355,10 +12367,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44959</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12387,10 +12399,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45029</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="C57" t="n">
@@ -12419,10 +12431,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45126</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12451,10 +12463,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="C59" t="n">
@@ -12483,10 +12495,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="C60" t="n">
@@ -12515,10 +12527,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45397</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="C61" t="n">
@@ -12547,10 +12559,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45489</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="C62" t="n">
@@ -12579,10 +12591,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45580</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="C63" t="n">
@@ -12611,10 +12623,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="C64" t="n">
@@ -12643,10 +12655,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45758</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="C65" t="n">
@@ -12675,10 +12687,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45852</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="C66" t="n">
@@ -12707,10 +12719,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45944</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="C67" t="n">
@@ -12739,10 +12751,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12771,10 +12783,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C69" t="n">
@@ -12803,10 +12815,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46217</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C70" t="n">
@@ -12853,12 +12865,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AXP.xlsx
+++ b/salidas/empresas/AXP.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>38.6201057434082</v>
+        <v>38.62009811401367</v>
       </c>
       <c r="C2" t="n">
         <v>52.45000076293945</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>39.67303085327148</v>
+        <v>39.67304992675781</v>
       </c>
       <c r="C3" t="n">
         <v>53.88000106811523</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.6937370300293</v>
+        <v>38.69373321533203</v>
       </c>
       <c r="C4" t="n">
         <v>52.54999923706055</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.11688995361328</v>
+        <v>40.11691665649414</v>
       </c>
       <c r="C6" t="n">
         <v>54.36000061035156</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.52722930908203</v>
+        <v>38.52724075317383</v>
       </c>
       <c r="C8" t="n">
         <v>52.06000137329102</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.8824577331543</v>
+        <v>38.88246154785156</v>
       </c>
       <c r="C9" t="n">
         <v>52.54000091552734</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>41.50226974487305</v>
+        <v>41.50225830078125</v>
       </c>
       <c r="C10" t="n">
         <v>56.08000183105469</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>43.57272720336914</v>
+        <v>43.57274627685547</v>
       </c>
       <c r="C12" t="n">
         <v>58.72000122070312</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.01971435546875</v>
+        <v>45.01969146728516</v>
       </c>
       <c r="C13" t="n">
         <v>60.66999816894531</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>43.30879592895508</v>
+        <v>43.30879211425781</v>
       </c>
       <c r="C14" t="n">
         <v>58.22000122070312</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.30454254150391</v>
+        <v>42.30454635620117</v>
       </c>
       <c r="C15" t="n">
         <v>56.86999893188477</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.95492553710938</v>
+        <v>41.95491027832031</v>
       </c>
       <c r="C16" t="n">
         <v>56.40000152587891</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>45.25281524658203</v>
+        <v>45.25281143188477</v>
       </c>
       <c r="C17" t="n">
         <v>60.66999816894531</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>48.46756362915039</v>
+        <v>48.46758651733398</v>
       </c>
       <c r="C18" t="n">
         <v>64.98000335693359</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.63321685791016</v>
+        <v>45.63322067260742</v>
       </c>
       <c r="C19" t="n">
         <v>61.18000030517578</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.77034759521484</v>
+        <v>43.77035140991211</v>
       </c>
       <c r="C20" t="n">
         <v>58.54000091552734</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>43.83016586303711</v>
+        <v>43.83015441894531</v>
       </c>
       <c r="C21" t="n">
         <v>58.61999893188477</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.20869827270508</v>
+        <v>44.20871734619141</v>
       </c>
       <c r="C24" t="n">
         <v>58.97999954223633</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>36.95346069335938</v>
+        <v>36.95346832275391</v>
       </c>
       <c r="C26" t="n">
         <v>49.13000106811523</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>31.81625175476074</v>
+        <v>31.81624031066895</v>
       </c>
       <c r="C27" t="n">
         <v>42.29999923706055</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>32.88430404663086</v>
+        <v>32.88430023193359</v>
       </c>
       <c r="C28" t="n">
         <v>43.72000122070312</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>34.99804306030273</v>
+        <v>34.998046875</v>
       </c>
       <c r="C30" t="n">
         <v>46.34999847412109</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.44392776489258</v>
+        <v>28.44393348693848</v>
       </c>
       <c r="C31" t="n">
         <v>37.66999816894531</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.15058326721191</v>
+        <v>28.15058898925781</v>
       </c>
       <c r="C32" t="n">
         <v>37.11999893188477</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>30.09202003479004</v>
+        <v>30.09200859069824</v>
       </c>
       <c r="C33" t="n">
         <v>39.68000030517578</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.86895751953125</v>
+        <v>26.86895561218262</v>
       </c>
       <c r="C34" t="n">
         <v>35.43000030517578</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.76780700683594</v>
+        <v>17.76780128479004</v>
       </c>
       <c r="C36" t="n">
         <v>23.30999946594238</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.13954925537109</v>
+        <v>14.13954448699951</v>
       </c>
       <c r="C37" t="n">
         <v>18.54999923706055</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.86214923858643</v>
+        <v>12.86215209960938</v>
       </c>
       <c r="C38" t="n">
         <v>16.72999954223633</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.271821022033691</v>
+        <v>9.271816253662109</v>
       </c>
       <c r="C39" t="n">
         <v>12.0600004196167</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.47884845733643</v>
+        <v>10.47884464263916</v>
       </c>
       <c r="C40" t="n">
         <v>13.63000011444092</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>19.64881706237793</v>
+        <v>19.64881134033203</v>
       </c>
       <c r="C41" t="n">
         <v>25.21999931335449</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.36054039001465</v>
+        <v>19.36054992675781</v>
       </c>
       <c r="C42" t="n">
         <v>24.85000038146973</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.23859024047852</v>
+        <v>22.23859214782715</v>
       </c>
       <c r="C44" t="n">
         <v>28.32999992370605</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>26.54814910888672</v>
+        <v>26.54815101623535</v>
       </c>
       <c r="C45" t="n">
         <v>33.81999969482422</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>26.75263023376465</v>
+        <v>26.75263404846191</v>
       </c>
       <c r="C46" t="n">
         <v>33.90000152587891</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.49442863464355</v>
+        <v>27.49443626403809</v>
       </c>
       <c r="C47" t="n">
         <v>34.84000015258789</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>33.01068496704102</v>
+        <v>33.01069641113281</v>
       </c>
       <c r="C48" t="n">
         <v>41.83000183105469</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>29.84938812255859</v>
+        <v>29.84938430786133</v>
       </c>
       <c r="C50" t="n">
         <v>37.65999984741211</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>30.26946067810059</v>
+        <v>30.26946258544922</v>
       </c>
       <c r="C51" t="n">
         <v>38.18999862670898</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.84527969360352</v>
+        <v>32.84526824951172</v>
       </c>
       <c r="C52" t="n">
         <v>41.2599983215332</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.71410751342773</v>
+        <v>36.71410369873047</v>
       </c>
       <c r="C53" t="n">
         <v>46.11999893188477</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.73876571655273</v>
+        <v>31.73874855041504</v>
       </c>
       <c r="C54" t="n">
         <v>39.86999893188477</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.74596214294434</v>
+        <v>31.74597358703613</v>
       </c>
       <c r="C55" t="n">
         <v>39.70000076293945</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>35.69620895385742</v>
+        <v>35.69621276855469</v>
       </c>
       <c r="C56" t="n">
         <v>44.63999938964844</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>31.88191223144531</v>
+        <v>31.88189506530762</v>
       </c>
       <c r="C57" t="n">
         <v>39.86999893188477</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.30998229980469</v>
+        <v>33.30997467041016</v>
       </c>
       <c r="C59" t="n">
         <v>41.45999908447266</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>34.72399139404297</v>
+        <v>34.7239875793457</v>
       </c>
       <c r="C60" t="n">
         <v>43.22000122070312</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.99587249755859</v>
+        <v>34.99586486816406</v>
       </c>
       <c r="C62" t="n">
         <v>43.38000106811523</v>
@@ -1788,7 +1788,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.464111328125</v>
+        <v>36.46410751342773</v>
       </c>
       <c r="C64" t="n">
         <v>45.20000076293945</v>
@@ -1817,7 +1817,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.75175857543945</v>
+        <v>39.75177001953125</v>
       </c>
       <c r="C65" t="n">
         <v>49.08000183105469</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>41.79280471801758</v>
+        <v>41.79280090332031</v>
       </c>
       <c r="C66" t="n">
         <v>51.59999847412109</v>
@@ -1875,7 +1875,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>42.025634765625</v>
+        <v>42.02563858032227</v>
       </c>
       <c r="C67" t="n">
         <v>51.70000076293945</v>
@@ -1904,7 +1904,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.67626190185547</v>
+        <v>40.67626571655273</v>
       </c>
       <c r="C68" t="n">
         <v>50.04000091552734</v>
@@ -1933,7 +1933,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.40800857543945</v>
+        <v>40.40801620483398</v>
       </c>
       <c r="C69" t="n">
         <v>49.70999908447266</v>
@@ -1962,7 +1962,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.49808502197266</v>
+        <v>36.49808883666992</v>
       </c>
       <c r="C70" t="n">
         <v>44.90000152587891</v>
@@ -1991,7 +1991,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.31897354125977</v>
+        <v>41.3189811706543</v>
       </c>
       <c r="C71" t="n">
         <v>50.61999893188477</v>
@@ -2020,7 +2020,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>39.21304702758789</v>
+        <v>39.21301651000977</v>
       </c>
       <c r="C72" t="n">
         <v>48.04000091552734</v>
@@ -2049,7 +2049,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>38.50288772583008</v>
+        <v>38.50288009643555</v>
       </c>
       <c r="C73" t="n">
         <v>47.16999816894531</v>
@@ -2078,7 +2078,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.07998275756836</v>
+        <v>41.07999038696289</v>
       </c>
       <c r="C74" t="n">
         <v>50.13999938964844</v>
@@ -2107,7 +2107,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>43.33306884765625</v>
+        <v>43.33308410644531</v>
       </c>
       <c r="C75" t="n">
         <v>52.88999938964844</v>
@@ -2136,7 +2136,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>47.40502548217773</v>
+        <v>47.40503311157227</v>
       </c>
       <c r="C76" t="n">
         <v>57.86000061035156</v>
@@ -2165,7 +2165,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.50106048583984</v>
+        <v>49.50107192993164</v>
       </c>
       <c r="C77" t="n">
         <v>60.20999908447266</v>
@@ -2194,7 +2194,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.90008163452148</v>
+        <v>45.90008926391602</v>
       </c>
       <c r="C78" t="n">
         <v>55.83000183105469</v>
@@ -2223,7 +2223,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>47.85676574707031</v>
+        <v>47.85677719116211</v>
       </c>
       <c r="C79" t="n">
         <v>58.20999908447266</v>
@@ -2310,7 +2310,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>46.90576171875</v>
+        <v>46.90577697753906</v>
       </c>
       <c r="C82" t="n">
         <v>56.86000061035156</v>
@@ -2339,7 +2339,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>46.3336181640625</v>
+        <v>46.33363342285156</v>
       </c>
       <c r="C83" t="n">
         <v>55.97000122070312</v>
@@ -2368,7 +2368,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>46.27568435668945</v>
+        <v>46.27567672729492</v>
       </c>
       <c r="C84" t="n">
         <v>55.90000152587891</v>
@@ -2397,7 +2397,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>47.58365631103516</v>
+        <v>47.58364486694336</v>
       </c>
       <c r="C85" t="n">
         <v>57.47999954223633</v>
@@ -2426,7 +2426,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.85466384887695</v>
+        <v>48.85465240478516</v>
       </c>
       <c r="C86" t="n">
         <v>58.81000137329102</v>
@@ -2484,7 +2484,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>56.04038238525391</v>
+        <v>56.04037857055664</v>
       </c>
       <c r="C88" t="n">
         <v>67.45999908447266</v>
@@ -2513,7 +2513,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>56.99810028076172</v>
+        <v>56.99811172485352</v>
       </c>
       <c r="C89" t="n">
         <v>68.41000366210938</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>63.08036804199219</v>
+        <v>63.08035659790039</v>
       </c>
       <c r="C90" t="n">
         <v>75.70999908447266</v>
@@ -2571,7 +2571,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>62.28879928588867</v>
+        <v>62.2888069152832</v>
       </c>
       <c r="C91" t="n">
         <v>74.76000213623047</v>
@@ -2600,7 +2600,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>61.65141677856445</v>
+        <v>61.65141296386719</v>
       </c>
       <c r="C92" t="n">
         <v>73.76999664306641</v>
@@ -2629,7 +2629,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>60.09699249267578</v>
+        <v>60.09698486328125</v>
       </c>
       <c r="C93" t="n">
         <v>71.91000366210938</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>63.11392593383789</v>
+        <v>63.11394500732422</v>
       </c>
       <c r="C94" t="n">
         <v>75.51999664306641</v>
@@ -2687,7 +2687,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>68.56999206542969</v>
+        <v>68.57000732421875</v>
       </c>
       <c r="C95" t="n">
         <v>81.80000305175781</v>
@@ -2712,7 +2712,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>71.92306518554688</v>
+        <v>71.92308044433594</v>
       </c>
       <c r="C96" t="n">
         <v>85.80000305175781</v>
@@ -2787,7 +2787,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>76.71420288085938</v>
+        <v>76.71417236328125</v>
       </c>
       <c r="C99" t="n">
         <v>91.27999877929688</v>
@@ -2816,7 +2816,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>75.66366577148438</v>
+        <v>75.66367340087891</v>
       </c>
       <c r="C100" t="n">
         <v>90.02999877929688</v>
@@ -2874,7 +2874,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>77.09355926513672</v>
+        <v>77.09358978271484</v>
       </c>
       <c r="C102" t="n">
         <v>91.5</v>
@@ -2932,7 +2932,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.34906768798828</v>
+        <v>74.34906005859375</v>
       </c>
       <c r="C104" t="n">
         <v>88</v>
@@ -2961,7 +2961,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>75.65863037109375</v>
+        <v>75.65859985351562</v>
       </c>
       <c r="C105" t="n">
         <v>89.55000305175781</v>
@@ -2990,7 +2990,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>73.96040344238281</v>
+        <v>73.96043395996094</v>
       </c>
       <c r="C106" t="n">
         <v>87.54000091552734</v>
@@ -3019,7 +3019,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.22293853759766</v>
+        <v>76.22296905517578</v>
       </c>
       <c r="C107" t="n">
         <v>89.94999694824219</v>
@@ -3048,7 +3048,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>78.31599426269531</v>
+        <v>78.31600952148438</v>
       </c>
       <c r="C108" t="n">
         <v>92.41999816894531</v>
@@ -3077,7 +3077,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>78.84138488769531</v>
+        <v>78.8414306640625</v>
       </c>
       <c r="C109" t="n">
         <v>93.04000091552734</v>
@@ -3106,7 +3106,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>68.57727813720703</v>
+        <v>68.5772705078125</v>
       </c>
       <c r="C110" t="n">
         <v>80.69000244140625</v>
@@ -3135,7 +3135,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>69.34214782714844</v>
+        <v>69.34215545654297</v>
       </c>
       <c r="C111" t="n">
         <v>81.58999633789062</v>
@@ -3164,7 +3164,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.61498260498047</v>
+        <v>66.614990234375</v>
       </c>
       <c r="C112" t="n">
         <v>78.12000274658203</v>
@@ -3193,7 +3193,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>66.04366302490234</v>
+        <v>66.04364776611328</v>
       </c>
       <c r="C113" t="n">
         <v>77.44999694824219</v>
@@ -3222,7 +3222,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>67.97930908203125</v>
+        <v>67.97933197021484</v>
       </c>
       <c r="C114" t="n">
         <v>79.72000122070312</v>
@@ -3251,7 +3251,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>66.52186584472656</v>
+        <v>66.52184295654297</v>
       </c>
       <c r="C115" t="n">
         <v>77.72000122070312</v>
@@ -3280,7 +3280,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>65.10100555419922</v>
+        <v>65.10102081298828</v>
       </c>
       <c r="C116" t="n">
         <v>76.05999755859375</v>
@@ -3309,7 +3309,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>65.66593170166016</v>
+        <v>65.66591644287109</v>
       </c>
       <c r="C117" t="n">
         <v>76.72000122070312</v>
@@ -3338,7 +3338,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>63.44909286499023</v>
+        <v>63.4490852355957</v>
       </c>
       <c r="C118" t="n">
         <v>74.12999725341797</v>
@@ -3396,7 +3396,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>61.54994201660156</v>
+        <v>61.54995727539062</v>
       </c>
       <c r="C120" t="n">
         <v>71.63999938964844</v>
@@ -3425,7 +3425,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>59.75429916381836</v>
+        <v>59.75431442260742</v>
       </c>
       <c r="C121" t="n">
         <v>69.55000305175781</v>
@@ -3454,7 +3454,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>46.16603469848633</v>
+        <v>46.1660270690918</v>
       </c>
       <c r="C122" t="n">
         <v>53.5</v>
@@ -3483,7 +3483,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>47.96089935302734</v>
+        <v>47.96090698242188</v>
       </c>
       <c r="C123" t="n">
         <v>55.58000183105469</v>
@@ -3512,7 +3512,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>52.98307418823242</v>
+        <v>52.98307037353516</v>
       </c>
       <c r="C124" t="n">
         <v>61.40000152587891</v>
@@ -3541,7 +3541,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>56.73399353027344</v>
+        <v>56.73397445678711</v>
       </c>
       <c r="C125" t="n">
         <v>65.43000030517578</v>
@@ -3570,7 +3570,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.02012634277344</v>
+        <v>57.0201301574707</v>
       </c>
       <c r="C126" t="n">
         <v>65.76000213623047</v>
@@ -3599,7 +3599,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>52.94984436035156</v>
+        <v>52.94985580444336</v>
       </c>
       <c r="C127" t="n">
         <v>60.7599983215332</v>
@@ -3628,7 +3628,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.17427062988281</v>
+        <v>56.17425155639648</v>
       </c>
       <c r="C128" t="n">
         <v>64.45999908447266</v>
@@ -3657,7 +3657,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>57.15028381347656</v>
+        <v>57.15029144287109</v>
       </c>
       <c r="C129" t="n">
         <v>65.58000183105469</v>
@@ -3686,7 +3686,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>55.80823516845703</v>
+        <v>55.80825042724609</v>
       </c>
       <c r="C130" t="n">
         <v>64.04000091552734</v>
@@ -3744,7 +3744,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.09584045410156</v>
+        <v>63.09585189819336</v>
       </c>
       <c r="C132" t="n">
         <v>72.04000091552734</v>
@@ -3773,7 +3773,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>64.88253784179688</v>
+        <v>64.88255310058594</v>
       </c>
       <c r="C133" t="n">
         <v>74.08000183105469</v>
@@ -3802,7 +3802,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>67.18229675292969</v>
+        <v>67.18230438232422</v>
       </c>
       <c r="C134" t="n">
         <v>76.37999725341797</v>
@@ -3831,7 +3831,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.419189453125</v>
+        <v>70.41915893554688</v>
       </c>
       <c r="C135" t="n">
         <v>80.05999755859375</v>
@@ -3860,7 +3860,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>69.58355712890625</v>
+        <v>69.58356475830078</v>
       </c>
       <c r="C136" t="n">
         <v>79.11000061035156</v>
@@ -3889,7 +3889,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>69.99288940429688</v>
+        <v>69.99289703369141</v>
       </c>
       <c r="C137" t="n">
         <v>79.25</v>
@@ -3947,7 +3947,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>74.40003204345703</v>
+        <v>74.40004730224609</v>
       </c>
       <c r="C139" t="n">
         <v>84.23999786376953</v>
@@ -3976,7 +3976,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>75.55854034423828</v>
+        <v>75.55850982666016</v>
       </c>
       <c r="C140" t="n">
         <v>85.23000335693359</v>
@@ -4005,7 +4005,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>76.32980346679688</v>
+        <v>76.32978820800781</v>
       </c>
       <c r="C141" t="n">
         <v>86.09999847412109</v>
@@ -4034,7 +4034,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>80.19501495361328</v>
+        <v>80.19503784179688</v>
       </c>
       <c r="C142" t="n">
         <v>90.45999908447266</v>
@@ -4092,7 +4092,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>86.95675659179688</v>
+        <v>86.95674896240234</v>
       </c>
       <c r="C144" t="n">
         <v>97.70999908447266</v>
@@ -4121,7 +4121,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>88.38064575195312</v>
+        <v>88.38065338134766</v>
       </c>
       <c r="C145" t="n">
         <v>99.30999755859375</v>
@@ -4150,7 +4150,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>88.77285766601562</v>
+        <v>88.77286529541016</v>
       </c>
       <c r="C146" t="n">
         <v>99.40000152587891</v>
@@ -4179,7 +4179,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>87.08494567871094</v>
+        <v>87.08492279052734</v>
       </c>
       <c r="C147" t="n">
         <v>97.51000213623047</v>
@@ -4266,7 +4266,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>88.12005615234375</v>
+        <v>88.12004852294922</v>
       </c>
       <c r="C150" t="n">
         <v>98.30000305175781</v>
@@ -4295,7 +4295,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>87.85111236572266</v>
+        <v>87.85112762451172</v>
       </c>
       <c r="C151" t="n">
         <v>98</v>
@@ -4324,7 +4324,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>89.53401184082031</v>
+        <v>89.53400421142578</v>
       </c>
       <c r="C152" t="n">
         <v>99.51999664306641</v>
@@ -4353,7 +4353,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>95.34580230712891</v>
+        <v>95.34580993652344</v>
       </c>
       <c r="C153" t="n">
         <v>105.9800033569336</v>
@@ -4382,7 +4382,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>95.80463409423828</v>
+        <v>95.80461120605469</v>
       </c>
       <c r="C154" t="n">
         <v>106.4899978637695</v>
@@ -4411,7 +4411,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>92.75547027587891</v>
+        <v>92.75548553466797</v>
       </c>
       <c r="C155" t="n">
         <v>102.7300033569336</v>
@@ -4440,7 +4440,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>101.3691864013672</v>
+        <v>101.3691940307617</v>
       </c>
       <c r="C156" t="n">
         <v>112.2699966430664</v>
@@ -4469,7 +4469,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>86.06492614746094</v>
+        <v>86.06494140625</v>
       </c>
       <c r="C157" t="n">
         <v>95.31999969482422</v>
@@ -4498,7 +4498,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>93.10788726806641</v>
+        <v>93.10791778564453</v>
       </c>
       <c r="C158" t="n">
         <v>102.6999969482422</v>
@@ -4527,7 +4527,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>97.67716217041016</v>
+        <v>97.67714691162109</v>
       </c>
       <c r="C159" t="n">
         <v>107.7399978637695</v>
@@ -4556,7 +4556,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>99.09147644042969</v>
+        <v>99.09144592285156</v>
       </c>
       <c r="C160" t="n">
         <v>109.3000030517578</v>
@@ -4614,7 +4614,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>104.3643264770508</v>
+        <v>104.3643035888672</v>
       </c>
       <c r="C162" t="n">
         <v>114.7099990844727</v>
@@ -4701,7 +4701,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>109.8563003540039</v>
+        <v>109.856315612793</v>
       </c>
       <c r="C165" t="n">
         <v>120.370002746582</v>
@@ -4730,7 +4730,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>107.9488525390625</v>
+        <v>107.9488677978516</v>
       </c>
       <c r="C166" t="n">
         <v>118.2799987792969</v>
@@ -4788,7 +4788,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>110.0474243164062</v>
+        <v>110.0474319458008</v>
       </c>
       <c r="C168" t="n">
         <v>120.120002746582</v>
@@ -4817,7 +4817,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>114.0510025024414</v>
+        <v>114.0509948730469</v>
       </c>
       <c r="C169" t="n">
         <v>124.4899978637695</v>
@@ -4846,7 +4846,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>119.3922576904297</v>
+        <v>119.3922500610352</v>
       </c>
       <c r="C170" t="n">
         <v>129.8699951171875</v>
@@ -4875,7 +4875,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>101.0609893798828</v>
+        <v>101.0609817504883</v>
       </c>
       <c r="C171" t="n">
         <v>109.9300003051758</v>
@@ -4904,7 +4904,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>78.70307159423828</v>
+        <v>78.70308685302734</v>
       </c>
       <c r="C172" t="n">
         <v>85.61000061035156</v>
@@ -4962,7 +4962,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>87.88536071777344</v>
+        <v>87.88535308837891</v>
       </c>
       <c r="C174" t="n">
         <v>95.06999969482422</v>
@@ -4991,7 +4991,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>88.00553894042969</v>
+        <v>88.00554656982422</v>
       </c>
       <c r="C175" t="n">
         <v>95.19999694824219</v>
@@ -5020,7 +5020,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>86.65904998779297</v>
+        <v>86.65903472900391</v>
       </c>
       <c r="C176" t="n">
         <v>93.31999969482422</v>
@@ -5049,7 +5049,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>94.33873748779297</v>
+        <v>94.3387451171875</v>
       </c>
       <c r="C177" t="n">
         <v>101.5899963378906</v>
@@ -5078,7 +5078,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>93.09438323974609</v>
+        <v>93.09437561035156</v>
       </c>
       <c r="C178" t="n">
         <v>100.25</v>
@@ -5107,7 +5107,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>85.08137512207031</v>
+        <v>85.08139801025391</v>
       </c>
       <c r="C179" t="n">
         <v>91.23999786376953</v>
@@ -5136,7 +5136,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>110.5852890014648</v>
+        <v>110.5852661132812</v>
       </c>
       <c r="C180" t="n">
         <v>118.5899963378906</v>
@@ -5194,7 +5194,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>108.7926940917969</v>
+        <v>108.7927093505859</v>
       </c>
       <c r="C182" t="n">
         <v>116.2600021362305</v>
@@ -5252,7 +5252,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.7532348632812</v>
+        <v>132.7532653808594</v>
       </c>
       <c r="C184" t="n">
         <v>141.4400024414062</v>
@@ -5281,7 +5281,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>143.9317779541016</v>
+        <v>143.9317932128906</v>
       </c>
       <c r="C185" t="n">
         <v>153.3500061035156</v>
@@ -5339,7 +5339,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>155.0820922851562</v>
+        <v>155.0821380615234</v>
       </c>
       <c r="C187" t="n">
         <v>165.2299957275391</v>
@@ -5368,7 +5368,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>160.4742736816406</v>
+        <v>160.4742431640625</v>
       </c>
       <c r="C188" t="n">
         <v>170.5299987792969</v>
@@ -5397,7 +5397,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>156.1737670898438</v>
+        <v>156.1737518310547</v>
       </c>
       <c r="C189" t="n">
         <v>165.9600067138672</v>
@@ -5426,7 +5426,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>157.6511077880859</v>
+        <v>157.6511688232422</v>
       </c>
       <c r="C190" t="n">
         <v>167.5299987792969</v>
@@ -5455,7 +5455,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>163.9391632080078</v>
+        <v>163.9391479492188</v>
       </c>
       <c r="C191" t="n">
         <v>173.7799987792969</v>
@@ -5513,7 +5513,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>154.3356323242188</v>
+        <v>154.3356475830078</v>
       </c>
       <c r="C193" t="n">
         <v>163.6000061035156</v>
@@ -5542,7 +5542,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>170.0628814697266</v>
+        <v>170.0628356933594</v>
       </c>
       <c r="C194" t="n">
         <v>179.8200073242188</v>
@@ -5571,7 +5571,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>183.984130859375</v>
+        <v>183.9841613769531</v>
       </c>
       <c r="C195" t="n">
         <v>194.5399932861328</v>
@@ -5600,7 +5600,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>176.8533020019531</v>
+        <v>176.853271484375</v>
       </c>
       <c r="C196" t="n">
         <v>187</v>
@@ -5629,7 +5629,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>165.6991729736328</v>
+        <v>165.6991882324219</v>
       </c>
       <c r="C197" t="n">
         <v>174.7100067138672</v>
@@ -5658,7 +5658,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>160.1129302978516</v>
+        <v>160.1129760742188</v>
       </c>
       <c r="C198" t="n">
         <v>168.8200073242188</v>
@@ -5716,7 +5716,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>146.6229248046875</v>
+        <v>146.6229400634766</v>
       </c>
       <c r="C200" t="n">
         <v>154.0200042724609</v>
@@ -5745,7 +5745,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>144.699951171875</v>
+        <v>144.6999206542969</v>
       </c>
       <c r="C201" t="n">
         <v>152</v>
@@ -5774,7 +5774,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>128.4307403564453</v>
+        <v>128.4307250976562</v>
       </c>
       <c r="C202" t="n">
         <v>134.9100036621094</v>
@@ -5803,7 +5803,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>141.8598785400391</v>
+        <v>141.8599090576172</v>
       </c>
       <c r="C203" t="n">
         <v>148.4499969482422</v>
@@ -5832,7 +5832,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>150.5941772460938</v>
+        <v>150.5941619873047</v>
       </c>
       <c r="C204" t="n">
         <v>157.5899963378906</v>
@@ -5861,7 +5861,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>141.1909942626953</v>
+        <v>141.1910095214844</v>
       </c>
       <c r="C205" t="n">
         <v>147.75</v>
@@ -5890,7 +5890,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>167.7437896728516</v>
+        <v>167.7438049316406</v>
       </c>
       <c r="C206" t="n">
         <v>174.9299926757812</v>
@@ -5948,7 +5948,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>158.1737823486328</v>
+        <v>158.1737976074219</v>
       </c>
       <c r="C208" t="n">
         <v>164.9499969482422</v>
@@ -5977,7 +5977,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>155.2852478027344</v>
+        <v>155.2852630615234</v>
       </c>
       <c r="C209" t="n">
         <v>161.3399963378906</v>
@@ -6035,7 +6035,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>167.6626586914062</v>
+        <v>167.6626281738281</v>
       </c>
       <c r="C211" t="n">
         <v>174.1999969482422</v>
@@ -6064,7 +6064,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>163.0996704101562</v>
+        <v>163.0996856689453</v>
       </c>
       <c r="C212" t="n">
         <v>168.8800048828125</v>
@@ -6122,7 +6122,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>144.0836181640625</v>
+        <v>144.0836029052734</v>
       </c>
       <c r="C214" t="n">
         <v>149.1900024414062</v>
@@ -6151,7 +6151,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>141.6112213134766</v>
+        <v>141.6112365722656</v>
       </c>
       <c r="C215" t="n">
         <v>146.0299987792969</v>
@@ -6209,7 +6209,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>181.6712341308594</v>
+        <v>181.6712036132812</v>
       </c>
       <c r="C217" t="n">
         <v>187.3399963378906</v>
@@ -6238,7 +6238,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>195.2946624755859</v>
+        <v>195.2946319580078</v>
       </c>
       <c r="C218" t="n">
         <v>200.7400054931641</v>
@@ -6354,7 +6354,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>234.2130584716797</v>
+        <v>234.2131195068359</v>
       </c>
       <c r="C222" t="n">
         <v>240</v>
@@ -6383,7 +6383,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>225.9668273925781</v>
+        <v>225.9668426513672</v>
       </c>
       <c r="C223" t="n">
         <v>231.5500030517578</v>
@@ -6412,7 +6412,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>247.6741790771484</v>
+        <v>247.6741943359375</v>
       </c>
       <c r="C224" t="n">
         <v>253.0399932861328</v>
@@ -6441,7 +6441,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>253.1652069091797</v>
+        <v>253.1651763916016</v>
       </c>
       <c r="C225" t="n">
         <v>258.6499938964844</v>
@@ -6470,7 +6470,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>265.4491577148438</v>
+        <v>265.4490966796875</v>
       </c>
       <c r="C226" t="n">
         <v>271.2000122070312</v>
@@ -6499,7 +6499,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>265.0435791015625</v>
+        <v>265.0436401367188</v>
       </c>
       <c r="C227" t="n">
         <v>270.0799865722656</v>
@@ -6586,7 +6586,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>312.2627258300781</v>
+        <v>312.2626953125</v>
       </c>
       <c r="C230" t="n">
         <v>317.4500122070312</v>
@@ -6615,7 +6615,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>296.0421447753906</v>
+        <v>296.0421752929688</v>
       </c>
       <c r="C231" t="n">
         <v>300.9599914550781</v>
@@ -6644,7 +6644,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>264.6536254882812</v>
+        <v>264.653564453125</v>
       </c>
       <c r="C232" t="n">
         <v>269.0499877929688</v>
@@ -6673,7 +6673,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>262.9266967773438</v>
+        <v>262.9267272949219</v>
       </c>
       <c r="C233" t="n">
         <v>266.4100036621094</v>
@@ -6731,7 +6731,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>314.8093872070312</v>
+        <v>314.8093566894531</v>
       </c>
       <c r="C235" t="n">
         <v>318.9800109863281</v>
@@ -6934,7 +6934,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>350.101806640625</v>
+        <v>350.1018371582031</v>
       </c>
       <c r="C242" t="n">
         <v>352.1700134277344</v>
